--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,24 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
   </si>
 </sst>
 </file>
@@ -521,16 +503,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>97.56</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -544,19 +526,19 @@
         <v>39</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>92.31</v>
+        <v>94.87</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -567,7 +549,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -576,10 +558,10 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5">
         <v>8.300000000000001</v>
@@ -635,16 +617,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.88</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -658,16 +643,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.56</v>
+      </c>
+      <c r="H3">
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -681,16 +669,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.44</v>
+      </c>
+      <c r="H4">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -701,19 +692,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.31999999999999</v>
+      </c>
+      <c r="H5">
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -769,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -804,7 +798,7 @@
         <v>97.56</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -818,19 +812,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -841,22 +835,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>28</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +860,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -896,52 +890,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920171</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920081</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
@@ -617,7 +617,7 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -629,7 +629,7 @@
         <v>96.88</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -763,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="H2">
         <v>8.5</v>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
@@ -798,7 +798,7 @@
         <v>97.56</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -815,16 +815,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>97.44</v>
+        <v>94.87</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
   </si>
 </sst>
 </file>
@@ -763,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>84.38</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -841,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>90.31999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -890,6 +899,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920162</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -79,10 +79,19 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>NERI</t>
+  </si>
+  <si>
     <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -869,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -907,10 +916,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -919,6 +928,29 @@
         <v>9</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920166</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>
